--- a/InputFiles/GC/TC04_GC_phs001787_SamTumSt-Normal_LibrStrtg-WXS_LibrSourMol-GenomicDNA.xlsx
+++ b/InputFiles/GC/TC04_GC_phs001787_SamTumSt-Normal_LibrStrtg-WXS_LibrSourMol-GenomicDNA.xlsx
@@ -538,6 +538,7 @@
         <is>
           <t xml:space="preserve">MATCH (samp:sample)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
 MATCH (gi:genomic_info)-[:of_file]-&gt;(f:file)-[:of_participant]-&gt;(p)
+MATCH (f)-[:from_sample]-&gt;(samp)
 WHERE s.phs_accession = "phs001787"
   AND gi.library_strategy = "WXS"
   AND samp.sample_tumor_status = "Normal"
